--- a/youzi/叶庆均/index.xlsx
+++ b/youzi/叶庆均/index.xlsx
@@ -39,43 +39,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF7CC98E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,37 +111,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,60 +183,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -273,67 +273,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1194,7 +1194,7 @@
       <c r="C2" t="str">
         <v>301563</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="2" t="str">
         <v>净买: 1249.35万</v>
       </c>
       <c r="E2">
@@ -1209,40 +1209,40 @@
       <c r="H2">
         <v>4.74</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="8">
         <v>-3.03</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="3">
         <v>-6.34</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="7">
         <v>-9.8</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="12">
         <v>-7.13</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="9">
         <v>-11.25</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="13">
         <v>-10.8</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="10">
         <v>-8.93</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="4">
         <v>-4.21</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="1">
         <v>-8.78</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="5">
         <v>-1.89</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="6">
         <v>-2.63</v>
       </c>
-      <c r="T2" s="8">
+      <c r="T2" s="11">
         <v>-12.7</v>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       <c r="C3" t="str">
         <v>002326</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="25" t="str">
         <v>净卖: -1394.43万</v>
       </c>
       <c r="E3">
@@ -1274,37 +1274,37 @@
       <c r="I3" s="26">
         <v>0</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="22">
         <v>-0.42</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="17">
         <v>-2.97</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="15">
         <v>-4.75</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="23">
         <v>-6.1</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="18">
         <v>-12.71</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="16">
         <v>-13.6</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="19">
         <v>-12.4</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="14">
         <v>-11.97</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="20">
         <v>-11.63</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="21">
         <v>-10.16</v>
       </c>
-      <c r="T3" s="16">
+      <c r="T3" s="24">
         <v>-4.71</v>
       </c>
     </row>
@@ -1367,40 +1367,40 @@
       <c r="F5" t="str"/>
       <c r="G5" t="str"/>
       <c r="H5" t="str"/>
-      <c r="I5" s="35">
+      <c r="I5" s="34">
         <v>0</v>
       </c>
-      <c r="J5" s="37">
+      <c r="J5" s="31">
         <v>0</v>
       </c>
-      <c r="K5" s="30">
+      <c r="K5" s="32">
         <v>0</v>
       </c>
-      <c r="L5" s="38">
+      <c r="L5" s="33">
         <v>0</v>
       </c>
-      <c r="M5" s="31">
+      <c r="M5" s="36">
         <v>0</v>
       </c>
-      <c r="N5" s="28">
+      <c r="N5" s="37">
         <v>0</v>
       </c>
-      <c r="O5" s="36">
+      <c r="O5" s="38">
         <v>0</v>
       </c>
-      <c r="P5" s="27">
+      <c r="P5" s="29">
         <v>0</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="35">
         <v>0</v>
       </c>
-      <c r="R5" s="32">
+      <c r="R5" s="27">
         <v>0</v>
       </c>
-      <c r="S5" s="33">
+      <c r="S5" s="28">
         <v>0</v>
       </c>
-      <c r="T5" s="34">
+      <c r="T5" s="30">
         <v>0</v>
       </c>
     </row>
@@ -1415,40 +1415,40 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="40">
+      <c r="I6" s="50">
         <v>-1.52</v>
       </c>
-      <c r="J6" s="43">
+      <c r="J6" s="42">
         <v>-3.38</v>
       </c>
-      <c r="K6" s="48">
+      <c r="K6" s="43">
         <v>-6.39</v>
       </c>
       <c r="L6" s="44">
         <v>-5.94</v>
       </c>
-      <c r="M6" s="46">
+      <c r="M6" s="47">
         <v>-8.68</v>
       </c>
-      <c r="N6" s="49">
+      <c r="N6" s="45">
         <v>-11.76</v>
       </c>
-      <c r="O6" s="45">
+      <c r="O6" s="39">
         <v>-11.27</v>
       </c>
-      <c r="P6" s="50">
+      <c r="P6" s="48">
         <v>-8.31</v>
       </c>
       <c r="Q6" s="41">
         <v>-10.38</v>
       </c>
-      <c r="R6" s="42">
+      <c r="R6" s="49">
         <v>-6.76</v>
       </c>
-      <c r="S6" s="39">
+      <c r="S6" s="40">
         <v>-6.4</v>
       </c>
-      <c r="T6" s="47">
+      <c r="T6" s="46">
         <v>-8.71</v>
       </c>
     </row>

--- a/youzi/叶庆均/index.xlsx
+++ b/youzi/叶庆均/index.xlsx
@@ -39,85 +39,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1C7A33"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,84 +195,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -315,25 +297,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF5BBC71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1194,7 +1194,7 @@
       <c r="C2" t="str">
         <v>301563</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="13" t="str">
         <v>净买: 1249.35万</v>
       </c>
       <c r="E2">
@@ -1209,40 +1209,40 @@
       <c r="H2">
         <v>4.74</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="1">
         <v>-3.03</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>-6.34</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="3">
         <v>-9.8</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="6">
         <v>-7.13</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="4">
         <v>-11.25</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="9">
         <v>-10.8</v>
       </c>
       <c r="O2" s="10">
         <v>-8.93</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="7">
         <v>-4.21</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="11">
         <v>-8.78</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="8">
         <v>-1.89</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="12">
         <v>-2.63</v>
       </c>
-      <c r="T2" s="11">
+      <c r="T2" s="5">
         <v>-12.7</v>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       <c r="C3" t="str">
         <v>002326</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="23" t="str">
         <v>净卖: -1394.43万</v>
       </c>
       <c r="E3">
@@ -1271,40 +1271,40 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="24">
         <v>0</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="19">
         <v>-0.42</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="16">
         <v>-2.97</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="25">
         <v>-4.75</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="18">
         <v>-6.1</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="20">
         <v>-12.71</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="21">
         <v>-13.6</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="26">
         <v>-12.4</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="22">
         <v>-11.97</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="14">
         <v>-11.63</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="17">
         <v>-10.16</v>
       </c>
-      <c r="T3" s="24">
+      <c r="T3" s="15">
         <v>-4.71</v>
       </c>
     </row>
@@ -1367,40 +1367,40 @@
       <c r="F5" t="str"/>
       <c r="G5" t="str"/>
       <c r="H5" t="str"/>
-      <c r="I5" s="34">
+      <c r="I5" s="36">
         <v>0</v>
       </c>
-      <c r="J5" s="31">
+      <c r="J5" s="37">
         <v>0</v>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="30">
         <v>0</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L5" s="31">
         <v>0</v>
       </c>
-      <c r="M5" s="36">
+      <c r="M5" s="33">
         <v>0</v>
       </c>
-      <c r="N5" s="37">
+      <c r="N5" s="38">
         <v>0</v>
       </c>
-      <c r="O5" s="38">
+      <c r="O5" s="27">
         <v>0</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="32">
         <v>0</v>
       </c>
-      <c r="Q5" s="35">
+      <c r="Q5" s="34">
         <v>0</v>
       </c>
-      <c r="R5" s="27">
+      <c r="R5" s="28">
         <v>0</v>
       </c>
-      <c r="S5" s="28">
+      <c r="S5" s="29">
         <v>0</v>
       </c>
-      <c r="T5" s="30">
+      <c r="T5" s="35">
         <v>0</v>
       </c>
     </row>
@@ -1415,40 +1415,40 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="50">
+      <c r="I6" s="44">
         <v>-1.52</v>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="39">
         <v>-3.38</v>
       </c>
-      <c r="K6" s="43">
+      <c r="K6" s="45">
         <v>-6.39</v>
       </c>
-      <c r="L6" s="44">
+      <c r="L6" s="46">
         <v>-5.94</v>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="48">
         <v>-8.68</v>
       </c>
-      <c r="N6" s="45">
+      <c r="N6" s="49">
         <v>-11.76</v>
       </c>
-      <c r="O6" s="39">
+      <c r="O6" s="40">
         <v>-11.27</v>
       </c>
-      <c r="P6" s="48">
+      <c r="P6" s="41">
         <v>-8.31</v>
       </c>
-      <c r="Q6" s="41">
+      <c r="Q6" s="42">
         <v>-10.38</v>
       </c>
-      <c r="R6" s="49">
+      <c r="R6" s="50">
         <v>-6.76</v>
       </c>
-      <c r="S6" s="40">
+      <c r="S6" s="43">
         <v>-6.4</v>
       </c>
-      <c r="T6" s="46">
+      <c r="T6" s="47">
         <v>-8.71</v>
       </c>
     </row>

--- a/youzi/叶庆均/index.xlsx
+++ b/youzi/叶庆均/index.xlsx
@@ -39,91 +39,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF7CC98E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF23973E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF218D3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,54 +183,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF32AB4E"/>
         <bgColor/>
       </patternFill>
@@ -297,43 +297,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1194,7 +1194,7 @@
       <c r="C2" t="str">
         <v>301563</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="10" t="str">
         <v>净买: 1249.35万</v>
       </c>
       <c r="E2">
@@ -1209,41 +1209,41 @@
       <c r="H2">
         <v>4.74</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="7">
         <v>-3.03</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="11">
         <v>-6.34</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="4">
         <v>-9.8</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="12">
         <v>-7.13</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="13">
         <v>-11.25</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="1">
         <v>-10.8</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="8">
         <v>-8.93</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="5">
         <v>-4.21</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="6">
         <v>-8.78</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="2">
         <v>-1.89</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="3">
         <v>-2.63</v>
       </c>
-      <c r="T2" s="5">
-        <v>-12.7</v>
+      <c r="T2" s="9">
+        <v>-13.96</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
       <c r="C3" t="str">
         <v>002326</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="22" t="str">
         <v>净卖: -1394.43万</v>
       </c>
       <c r="E3">
@@ -1271,41 +1271,41 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="18">
         <v>0</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="23">
         <v>-0.42</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="24">
         <v>-2.97</v>
       </c>
       <c r="L3" s="25">
         <v>-4.75</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="16">
         <v>-6.1</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="17">
         <v>-12.71</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="20">
         <v>-13.6</v>
       </c>
       <c r="P3" s="26">
         <v>-12.4</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="14">
         <v>-11.97</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="19">
         <v>-11.63</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="15">
         <v>-10.16</v>
       </c>
-      <c r="T3" s="15">
-        <v>-4.71</v>
+      <c r="T3" s="21">
+        <v>-5.25</v>
       </c>
     </row>
     <row r="4">
@@ -1367,40 +1367,40 @@
       <c r="F5" t="str"/>
       <c r="G5" t="str"/>
       <c r="H5" t="str"/>
-      <c r="I5" s="36">
+      <c r="I5" s="33">
         <v>0</v>
       </c>
-      <c r="J5" s="37">
+      <c r="J5" s="30">
         <v>0</v>
       </c>
-      <c r="K5" s="30">
+      <c r="K5" s="31">
         <v>0</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="37">
         <v>0</v>
       </c>
-      <c r="M5" s="33">
+      <c r="M5" s="38">
         <v>0</v>
       </c>
-      <c r="N5" s="38">
+      <c r="N5" s="28">
         <v>0</v>
       </c>
-      <c r="O5" s="27">
+      <c r="O5" s="34">
         <v>0</v>
       </c>
-      <c r="P5" s="32">
+      <c r="P5" s="35">
         <v>0</v>
       </c>
-      <c r="Q5" s="34">
+      <c r="Q5" s="32">
         <v>0</v>
       </c>
-      <c r="R5" s="28">
+      <c r="R5" s="29">
         <v>0</v>
       </c>
-      <c r="S5" s="29">
+      <c r="S5" s="36">
         <v>0</v>
       </c>
-      <c r="T5" s="35">
+      <c r="T5" s="27">
         <v>0</v>
       </c>
     </row>
@@ -1415,41 +1415,41 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="44">
+      <c r="I6" s="50">
         <v>-1.52</v>
       </c>
       <c r="J6" s="39">
         <v>-3.38</v>
       </c>
-      <c r="K6" s="45">
+      <c r="K6" s="48">
         <v>-6.39</v>
       </c>
-      <c r="L6" s="46">
+      <c r="L6" s="40">
         <v>-5.94</v>
       </c>
-      <c r="M6" s="48">
+      <c r="M6" s="41">
         <v>-8.68</v>
       </c>
       <c r="N6" s="49">
         <v>-11.76</v>
       </c>
-      <c r="O6" s="40">
+      <c r="O6" s="43">
         <v>-11.27</v>
       </c>
-      <c r="P6" s="41">
+      <c r="P6" s="44">
         <v>-8.31</v>
       </c>
-      <c r="Q6" s="42">
+      <c r="Q6" s="45">
         <v>-10.38</v>
       </c>
-      <c r="R6" s="50">
+      <c r="R6" s="46">
         <v>-6.76</v>
       </c>
-      <c r="S6" s="43">
+      <c r="S6" s="42">
         <v>-6.4</v>
       </c>
       <c r="T6" s="47">
-        <v>-8.71</v>
+        <v>-9.61</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/叶庆均/index.xlsx
+++ b/youzi/叶庆均/index.xlsx
@@ -39,7 +39,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -51,79 +63,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF8DD09D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF4DB665"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,25 +153,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
+        <fgColor rgb="FF32AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,67 +177,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF7FCA90"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBC71"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -274,66 +334,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBC71"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1194,7 +1194,7 @@
       <c r="C2" t="str">
         <v>301563</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="5" t="str">
         <v>净买: 1249.35万</v>
       </c>
       <c r="E2">
@@ -1209,41 +1209,41 @@
       <c r="H2">
         <v>4.74</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="1">
         <v>-3.03</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="2">
         <v>-6.34</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="3">
         <v>-9.8</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="11">
         <v>-7.13</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="6">
         <v>-11.25</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="7">
         <v>-10.8</v>
       </c>
       <c r="O2" s="8">
         <v>-8.93</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="12">
         <v>-4.21</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="9">
         <v>-8.78</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="4">
         <v>-1.89</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="13">
         <v>-2.63</v>
       </c>
-      <c r="T2" s="9">
-        <v>-13.96</v>
+      <c r="T2" s="10">
+        <v>-13.39</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
       <c r="C3" t="str">
         <v>002326</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="23" t="str">
         <v>净卖: -1394.43万</v>
       </c>
       <c r="E3">
@@ -1271,31 +1271,31 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="16">
         <v>0</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="17">
         <v>-0.42</v>
       </c>
       <c r="K3" s="24">
         <v>-2.97</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="20">
         <v>-4.75</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="18">
         <v>-6.1</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="21">
         <v>-12.71</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="22">
         <v>-13.6</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="25">
         <v>-12.4</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="26">
         <v>-11.97</v>
       </c>
       <c r="R3" s="19">
@@ -1304,8 +1304,8 @@
       <c r="S3" s="15">
         <v>-10.16</v>
       </c>
-      <c r="T3" s="21">
-        <v>-5.25</v>
+      <c r="T3" s="14">
+        <v>-4.13</v>
       </c>
     </row>
     <row r="4">
@@ -1367,40 +1367,40 @@
       <c r="F5" t="str"/>
       <c r="G5" t="str"/>
       <c r="H5" t="str"/>
-      <c r="I5" s="33">
+      <c r="I5" s="38">
         <v>0</v>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="33">
         <v>0</v>
       </c>
-      <c r="K5" s="31">
+      <c r="K5" s="35">
         <v>0</v>
       </c>
-      <c r="L5" s="37">
+      <c r="L5" s="27">
         <v>0</v>
       </c>
-      <c r="M5" s="38">
+      <c r="M5" s="28">
         <v>0</v>
       </c>
-      <c r="N5" s="28">
+      <c r="N5" s="32">
         <v>0</v>
       </c>
-      <c r="O5" s="34">
+      <c r="O5" s="29">
         <v>0</v>
       </c>
-      <c r="P5" s="35">
+      <c r="P5" s="36">
         <v>0</v>
       </c>
-      <c r="Q5" s="32">
+      <c r="Q5" s="34">
         <v>0</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="30">
         <v>0</v>
       </c>
-      <c r="S5" s="36">
+      <c r="S5" s="37">
         <v>0</v>
       </c>
-      <c r="T5" s="27">
+      <c r="T5" s="31">
         <v>0</v>
       </c>
     </row>
@@ -1415,28 +1415,28 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="50">
+      <c r="I6" s="43">
         <v>-1.52</v>
       </c>
-      <c r="J6" s="39">
+      <c r="J6" s="49">
         <v>-3.38</v>
       </c>
-      <c r="K6" s="48">
+      <c r="K6" s="50">
         <v>-6.39</v>
       </c>
-      <c r="L6" s="40">
+      <c r="L6" s="39">
         <v>-5.94</v>
       </c>
-      <c r="M6" s="41">
+      <c r="M6" s="40">
         <v>-8.68</v>
       </c>
-      <c r="N6" s="49">
+      <c r="N6" s="44">
         <v>-11.76</v>
       </c>
-      <c r="O6" s="43">
+      <c r="O6" s="41">
         <v>-11.27</v>
       </c>
-      <c r="P6" s="44">
+      <c r="P6" s="47">
         <v>-8.31</v>
       </c>
       <c r="Q6" s="45">
@@ -1445,11 +1445,11 @@
       <c r="R6" s="46">
         <v>-6.76</v>
       </c>
-      <c r="S6" s="42">
+      <c r="S6" s="48">
         <v>-6.4</v>
       </c>
-      <c r="T6" s="47">
-        <v>-9.61</v>
+      <c r="T6" s="42">
+        <v>-8.76</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/叶庆均/index.xlsx
+++ b/youzi/叶庆均/index.xlsx
@@ -45,19 +45,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF23973E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,55 +123,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4DB665"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,19 +171,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF7FCA90"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,97 +195,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -310,24 +328,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1194,7 +1194,7 @@
       <c r="C2" t="str">
         <v>301563</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="13" t="str">
         <v>净买: 1249.35万</v>
       </c>
       <c r="E2">
@@ -1212,13 +1212,13 @@
       <c r="I2" s="1">
         <v>-3.03</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="11">
         <v>-6.34</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="2">
         <v>-9.8</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="5">
         <v>-7.13</v>
       </c>
       <c r="M2" s="6">
@@ -1230,20 +1230,20 @@
       <c r="O2" s="8">
         <v>-8.93</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="3">
         <v>-4.21</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="4">
         <v>-8.78</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="9">
         <v>-1.89</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="10">
         <v>-2.63</v>
       </c>
-      <c r="T2" s="10">
-        <v>-13.39</v>
+      <c r="T2" s="12">
+        <v>-15.19</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
       <c r="C3" t="str">
         <v>002326</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="15" t="str">
         <v>净卖: -1394.43万</v>
       </c>
       <c r="E3">
@@ -1271,41 +1271,41 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="22">
         <v>0</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="16">
         <v>-0.42</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="23">
         <v>-2.97</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="24">
         <v>-4.75</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="17">
         <v>-6.1</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="25">
         <v>-12.71</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="18">
         <v>-13.6</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="26">
         <v>-12.4</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="19">
         <v>-11.97</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="20">
         <v>-11.63</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="14">
         <v>-10.16</v>
       </c>
-      <c r="T3" s="14">
-        <v>-4.13</v>
+      <c r="T3" s="21">
+        <v>1.27</v>
       </c>
     </row>
     <row r="4">
@@ -1367,41 +1367,41 @@
       <c r="F5" t="str"/>
       <c r="G5" t="str"/>
       <c r="H5" t="str"/>
-      <c r="I5" s="38">
+      <c r="I5" s="36">
         <v>0</v>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="27">
         <v>0</v>
       </c>
-      <c r="K5" s="35">
+      <c r="K5" s="29">
         <v>0</v>
       </c>
-      <c r="L5" s="27">
+      <c r="L5" s="31">
         <v>0</v>
       </c>
-      <c r="M5" s="28">
+      <c r="M5" s="32">
         <v>0</v>
       </c>
-      <c r="N5" s="32">
+      <c r="N5" s="37">
         <v>0</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="33">
         <v>0</v>
       </c>
-      <c r="P5" s="36">
+      <c r="P5" s="34">
         <v>0</v>
       </c>
-      <c r="Q5" s="34">
+      <c r="Q5" s="30">
         <v>0</v>
       </c>
-      <c r="R5" s="30">
+      <c r="R5" s="28">
         <v>0</v>
       </c>
-      <c r="S5" s="37">
+      <c r="S5" s="38">
         <v>0</v>
       </c>
-      <c r="T5" s="31">
-        <v>0</v>
+      <c r="T5" s="35">
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -1415,41 +1415,41 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="43">
+      <c r="I6" s="46">
         <v>-1.52</v>
       </c>
-      <c r="J6" s="49">
+      <c r="J6" s="41">
         <v>-3.38</v>
       </c>
-      <c r="K6" s="50">
+      <c r="K6" s="42">
         <v>-6.39</v>
       </c>
-      <c r="L6" s="39">
+      <c r="L6" s="48">
         <v>-5.94</v>
       </c>
-      <c r="M6" s="40">
+      <c r="M6" s="49">
         <v>-8.68</v>
       </c>
-      <c r="N6" s="44">
+      <c r="N6" s="50">
         <v>-11.76</v>
       </c>
-      <c r="O6" s="41">
+      <c r="O6" s="43">
         <v>-11.27</v>
       </c>
-      <c r="P6" s="47">
+      <c r="P6" s="44">
         <v>-8.31</v>
       </c>
-      <c r="Q6" s="45">
+      <c r="Q6" s="39">
         <v>-10.38</v>
       </c>
-      <c r="R6" s="46">
+      <c r="R6" s="45">
         <v>-6.76</v>
       </c>
-      <c r="S6" s="48">
+      <c r="S6" s="47">
         <v>-6.4</v>
       </c>
-      <c r="T6" s="42">
-        <v>-8.76</v>
+      <c r="T6" s="40">
+        <v>-6.96</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/叶庆均/index.xlsx
+++ b/youzi/叶庆均/index.xlsx
@@ -39,19 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF7CC98E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196E2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,78 +117,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFECF7EF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF249A3F"/>
         <bgColor/>
       </patternFill>
@@ -159,7 +177,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,31 +189,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFDA3444"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,37 +273,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBC71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBC71"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1194,7 +1194,7 @@
       <c r="C2" t="str">
         <v>301563</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="3" t="str">
         <v>净买: 1249.35万</v>
       </c>
       <c r="E2">
@@ -1209,41 +1209,41 @@
       <c r="H2">
         <v>4.74</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="4">
         <v>-3.03</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="7">
         <v>-6.34</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="9">
         <v>-9.8</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="12">
         <v>-7.13</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="10">
         <v>-11.25</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="5">
         <v>-10.8</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="11">
         <v>-8.93</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="6">
         <v>-4.21</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="13">
         <v>-8.78</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="8">
         <v>-1.89</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="1">
         <v>-2.63</v>
       </c>
-      <c r="T2" s="12">
-        <v>-15.19</v>
+      <c r="T2" s="2">
+        <v>-14.27</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
       <c r="C3" t="str">
         <v>002326</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="14" t="str">
         <v>净卖: -1394.43万</v>
       </c>
       <c r="E3">
@@ -1271,41 +1271,41 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="25">
         <v>0</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="17">
         <v>-0.42</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="18">
         <v>-2.97</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="19">
         <v>-4.75</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="20">
         <v>-6.1</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="21">
         <v>-12.71</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="22">
         <v>-13.6</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="23">
         <v>-12.4</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="24">
         <v>-11.97</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="15">
         <v>-11.63</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="16">
         <v>-10.16</v>
       </c>
-      <c r="T3" s="21">
-        <v>1.27</v>
+      <c r="T3" s="26">
+        <v>5.14</v>
       </c>
     </row>
     <row r="4">
@@ -1367,40 +1367,40 @@
       <c r="F5" t="str"/>
       <c r="G5" t="str"/>
       <c r="H5" t="str"/>
-      <c r="I5" s="36">
+      <c r="I5" s="37">
         <v>0</v>
       </c>
-      <c r="J5" s="27">
+      <c r="J5" s="29">
         <v>0</v>
       </c>
-      <c r="K5" s="29">
+      <c r="K5" s="35">
         <v>0</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="30">
         <v>0</v>
       </c>
-      <c r="M5" s="32">
+      <c r="M5" s="31">
         <v>0</v>
       </c>
-      <c r="N5" s="37">
+      <c r="N5" s="33">
         <v>0</v>
       </c>
-      <c r="O5" s="33">
+      <c r="O5" s="38">
         <v>0</v>
       </c>
-      <c r="P5" s="34">
+      <c r="P5" s="27">
         <v>0</v>
       </c>
-      <c r="Q5" s="30">
+      <c r="Q5" s="36">
         <v>0</v>
       </c>
       <c r="R5" s="28">
         <v>0</v>
       </c>
-      <c r="S5" s="38">
+      <c r="S5" s="32">
         <v>0</v>
       </c>
-      <c r="T5" s="35">
+      <c r="T5" s="34">
         <v>50</v>
       </c>
     </row>
@@ -1415,41 +1415,41 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="46">
+      <c r="I6" s="41">
         <v>-1.52</v>
       </c>
-      <c r="J6" s="41">
+      <c r="J6" s="46">
         <v>-3.38</v>
       </c>
-      <c r="K6" s="42">
+      <c r="K6" s="47">
         <v>-6.39</v>
       </c>
-      <c r="L6" s="48">
+      <c r="L6" s="42">
         <v>-5.94</v>
       </c>
-      <c r="M6" s="49">
+      <c r="M6" s="43">
         <v>-8.68</v>
       </c>
       <c r="N6" s="50">
         <v>-11.76</v>
       </c>
-      <c r="O6" s="43">
+      <c r="O6" s="48">
         <v>-11.27</v>
       </c>
       <c r="P6" s="44">
         <v>-8.31</v>
       </c>
-      <c r="Q6" s="39">
+      <c r="Q6" s="49">
         <v>-10.38</v>
       </c>
-      <c r="R6" s="45">
+      <c r="R6" s="39">
         <v>-6.76</v>
       </c>
-      <c r="S6" s="47">
+      <c r="S6" s="40">
         <v>-6.4</v>
       </c>
-      <c r="T6" s="40">
-        <v>-6.96</v>
+      <c r="T6" s="45">
+        <v>-4.56</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/叶庆均/index.xlsx
+++ b/youzi/叶庆均/index.xlsx
@@ -39,19 +39,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF8DD09D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,25 +93,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,25 +111,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF218D3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,133 +177,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF32AB4E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -280,60 +334,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1194,7 +1194,7 @@
       <c r="C2" t="str">
         <v>301563</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="2" t="str">
         <v>净买: 1249.35万</v>
       </c>
       <c r="E2">
@@ -1209,41 +1209,41 @@
       <c r="H2">
         <v>4.74</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="9">
         <v>-3.03</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>-6.34</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="12">
         <v>-9.8</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="13">
         <v>-7.13</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="3">
         <v>-11.25</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="4">
         <v>-10.8</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="10">
         <v>-8.93</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="7">
         <v>-4.21</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="11">
         <v>-8.78</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="1">
         <v>-1.89</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="5">
         <v>-2.63</v>
       </c>
-      <c r="T2" s="2">
-        <v>-14.27</v>
+      <c r="T2" s="8">
+        <v>-16.03</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
       <c r="C3" t="str">
         <v>002326</v>
       </c>
-      <c r="D3" s="14" t="str">
+      <c r="D3" s="23" t="str">
         <v>净卖: -1394.43万</v>
       </c>
       <c r="E3">
@@ -1271,41 +1271,41 @@
       <c r="H3">
         <v>-10.01</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="16">
         <v>0</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="19">
         <v>-0.42</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="20">
         <v>-2.97</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="24">
         <v>-4.75</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="22">
         <v>-6.1</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="25">
         <v>-12.71</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="26">
         <v>-13.6</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="17">
         <v>-12.4</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="14">
         <v>-11.97</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="21">
         <v>-11.63</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="18">
         <v>-10.16</v>
       </c>
-      <c r="T3" s="26">
-        <v>5.14</v>
+      <c r="T3" s="15">
+        <v>-5.37</v>
       </c>
     </row>
     <row r="4">
@@ -1367,41 +1367,41 @@
       <c r="F5" t="str"/>
       <c r="G5" t="str"/>
       <c r="H5" t="str"/>
-      <c r="I5" s="37">
+      <c r="I5" s="27">
         <v>0</v>
       </c>
-      <c r="J5" s="29">
+      <c r="J5" s="30">
         <v>0</v>
       </c>
-      <c r="K5" s="35">
+      <c r="K5" s="28">
         <v>0</v>
       </c>
-      <c r="L5" s="30">
+      <c r="L5" s="31">
         <v>0</v>
       </c>
-      <c r="M5" s="31">
+      <c r="M5" s="36">
         <v>0</v>
       </c>
-      <c r="N5" s="33">
+      <c r="N5" s="37">
         <v>0</v>
       </c>
-      <c r="O5" s="38">
+      <c r="O5" s="32">
         <v>0</v>
       </c>
-      <c r="P5" s="27">
+      <c r="P5" s="38">
         <v>0</v>
       </c>
-      <c r="Q5" s="36">
+      <c r="Q5" s="29">
         <v>0</v>
       </c>
-      <c r="R5" s="28">
+      <c r="R5" s="33">
         <v>0</v>
       </c>
-      <c r="S5" s="32">
+      <c r="S5" s="34">
         <v>0</v>
       </c>
-      <c r="T5" s="34">
-        <v>50</v>
+      <c r="T5" s="35">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1415,41 +1415,41 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="41">
+      <c r="I6" s="50">
         <v>-1.52</v>
       </c>
-      <c r="J6" s="46">
+      <c r="J6" s="45">
         <v>-3.38</v>
       </c>
-      <c r="K6" s="47">
+      <c r="K6" s="43">
         <v>-6.39</v>
       </c>
-      <c r="L6" s="42">
+      <c r="L6" s="46">
         <v>-5.94</v>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="47">
         <v>-8.68</v>
       </c>
-      <c r="N6" s="50">
+      <c r="N6" s="40">
         <v>-11.76</v>
       </c>
-      <c r="O6" s="48">
+      <c r="O6" s="41">
         <v>-11.27</v>
       </c>
-      <c r="P6" s="44">
+      <c r="P6" s="48">
         <v>-8.31</v>
       </c>
-      <c r="Q6" s="49">
+      <c r="Q6" s="44">
         <v>-10.38</v>
       </c>
-      <c r="R6" s="39">
+      <c r="R6" s="49">
         <v>-6.76</v>
       </c>
-      <c r="S6" s="40">
+      <c r="S6" s="42">
         <v>-6.4</v>
       </c>
-      <c r="T6" s="45">
-        <v>-4.56</v>
+      <c r="T6" s="39">
+        <v>-10.7</v>
       </c>
     </row>
   </sheetData>
